--- a/Daily_Practice/Day7_TEXT_microProject.xlsx
+++ b/Daily_Practice/Day7_TEXT_microProject.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BE72FBD-1B71-4290-93F9-7CFEAEF4C5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AA2772E-221C-4685-835B-12E9E27828E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -502,6 +502,9 @@
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1300,15 +1303,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>866775</xdr:colOff>
+      <xdr:colOff>828675</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1449,7 +1452,7 @@
   <dimension ref="A1:BX85"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="34.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="28" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="34.140625" style="2" customWidth="1"/>
@@ -1911,7 +1914,10 @@
       <c r="D12" s="11" t="str">
         <v>DataBricks</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="10">
+        <f>COUNTIF($B$11:$B$85,$C12)</f>
+        <v>12</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
